--- a/flask_project/uploads/data.xlsx
+++ b/flask_project/uploads/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Park_Chou\Desktop\實習生整合版\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Park_Chou\Desktop\flask_project\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAAF99AD-6612-4A2F-8136-3F8C2BB02E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB7A120-059F-430B-957C-65E9567D77D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="17">
+  <futureMetadata name="XLRICHVALUE" count="18">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -164,8 +164,15 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="17"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="17">
+  <valueMetadata count="18">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -216,6 +223,9 @@
     </bk>
     <bk>
       <rc t="1" v="16"/>
+    </bk>
+    <bk>
+      <rc t="1" v="17"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -1486,12 +1496,33 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1512,31 +1543,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1545,14 +1552,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1794,7 +1804,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="17">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="18">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -1863,6 +1873,10 @@
     <v>16</v>
     <v>5</v>
   </rv>
+  <rv s="0">
+    <v>17</v>
+    <v>5</v>
+  </rv>
 </rvData>
 </file>
 
@@ -1894,6 +1908,7 @@
   <rel r:id="rId15"/>
   <rel r:id="rId16"/>
   <rel r:id="rId17"/>
+  <rel r:id="rId18"/>
 </richValueRels>
 </file>
 
@@ -2179,10 +2194,10 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="31">
+      <c r="A2" s="38">
         <v>1</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="36" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -2190,8 +2205,8 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="330.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="32"/>
-      <c r="B3" s="38"/>
+      <c r="A3" s="39"/>
+      <c r="B3" s="37"/>
       <c r="C3" s="8" t="s">
         <v>85</v>
       </c>
@@ -2200,10 +2215,10 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="31">
+      <c r="A4" s="38">
         <v>2</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="36" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="7" t="s">
@@ -2211,8 +2226,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="230.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="32"/>
-      <c r="B5" s="38"/>
+      <c r="A5" s="39"/>
+      <c r="B5" s="37"/>
       <c r="C5" s="14" t="s">
         <v>87</v>
       </c>
@@ -2221,10 +2236,10 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="31">
+      <c r="A6" s="38">
         <v>3</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="36" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="7" t="s">
@@ -2232,17 +2247,20 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="32"/>
-      <c r="B7" s="38"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="37"/>
       <c r="C7" s="8" t="s">
         <v>89</v>
       </c>
+      <c r="D7" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="8" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="31">
+      <c r="A8" s="38">
         <v>4</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="40" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="23" t="s">
@@ -2250,17 +2268,17 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="32"/>
-      <c r="B9" s="34"/>
+      <c r="A9" s="39"/>
+      <c r="B9" s="41"/>
       <c r="C9" s="24" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="35">
+      <c r="A10" s="42">
         <v>5</v>
       </c>
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="43" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="6" t="s">
@@ -2268,17 +2286,17 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="195" x14ac:dyDescent="0.25">
-      <c r="A11" s="28"/>
-      <c r="B11" s="29"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="44"/>
       <c r="C11" s="16" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="28">
+      <c r="A12" s="30">
         <v>6</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="44" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="6" t="s">
@@ -2286,17 +2304,17 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
-      <c r="B13" s="29"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="44"/>
       <c r="C13" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="28">
+      <c r="A14" s="30">
         <v>7</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="28" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -2304,17 +2322,17 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="A15" s="28"/>
-      <c r="B15" s="30"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="28"/>
       <c r="C15" s="16" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28">
+      <c r="A16" s="30">
         <v>8</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="44" t="s">
         <v>19</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -2322,17 +2340,17 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
-      <c r="B17" s="29"/>
+      <c r="A17" s="30"/>
+      <c r="B17" s="44"/>
       <c r="C17" s="17" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="28">
+      <c r="A18" s="30">
         <v>9</v>
       </c>
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="28" t="s">
         <v>20</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -2340,17 +2358,17 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
-      <c r="B19" s="30"/>
+      <c r="A19" s="30"/>
+      <c r="B19" s="28"/>
       <c r="C19" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="28">
+      <c r="A20" s="30">
         <v>10</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="44" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -2358,17 +2376,17 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="28"/>
-      <c r="B21" s="29"/>
+      <c r="A21" s="30"/>
+      <c r="B21" s="44"/>
       <c r="C21" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="28">
+      <c r="A22" s="30">
         <v>11</v>
       </c>
-      <c r="B22" s="30" t="s">
+      <c r="B22" s="28" t="s">
         <v>25</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -2376,17 +2394,17 @@
       </c>
     </row>
     <row r="23" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A23" s="28"/>
-      <c r="B23" s="30"/>
+      <c r="A23" s="30"/>
+      <c r="B23" s="28"/>
       <c r="C23" s="16" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="28">
+      <c r="A24" s="30">
         <v>12</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="28" t="s">
         <v>26</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -2394,17 +2412,17 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="190.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="28"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="18" t="e" vm="3">
+      <c r="A25" s="30"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="18" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="28">
+      <c r="A26" s="30">
         <v>13</v>
       </c>
-      <c r="B26" s="30" t="s">
+      <c r="B26" s="28" t="s">
         <v>39</v>
       </c>
       <c r="C26" s="3" t="s">
@@ -2412,20 +2430,20 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="276.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="28"/>
-      <c r="B27" s="30"/>
+      <c r="A27" s="30"/>
+      <c r="B27" s="28"/>
       <c r="C27" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D27" s="15" t="e" vm="4">
+      <c r="D27" s="15" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="28">
+      <c r="A28" s="30">
         <v>14</v>
       </c>
-      <c r="B28" s="30" t="s">
+      <c r="B28" s="28" t="s">
         <v>44</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -2433,17 +2451,17 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="28"/>
-      <c r="B29" s="30"/>
+      <c r="A29" s="30"/>
+      <c r="B29" s="28"/>
       <c r="C29" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="28">
+      <c r="A30" s="30">
         <v>15</v>
       </c>
-      <c r="B30" s="40" t="s">
+      <c r="B30" s="31" t="s">
         <v>46</v>
       </c>
       <c r="C30" s="25" t="s">
@@ -2451,20 +2469,20 @@
       </c>
     </row>
     <row r="31" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="28"/>
-      <c r="B31" s="40"/>
+      <c r="A31" s="30"/>
+      <c r="B31" s="31"/>
       <c r="C31" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="D31" t="e" vm="5">
+      <c r="D31" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="44">
+      <c r="A32" s="35">
         <v>16</v>
       </c>
-      <c r="B32" s="41" t="s">
+      <c r="B32" s="32" t="s">
         <v>82</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -2472,31 +2490,31 @@
       </c>
     </row>
     <row r="33" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="39"/>
-      <c r="B33" s="42"/>
+      <c r="A33" s="29"/>
+      <c r="B33" s="33"/>
       <c r="C33" s="19" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="39"/>
-      <c r="B34" s="42"/>
+      <c r="A34" s="29"/>
+      <c r="B34" s="33"/>
       <c r="C34" s="19" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A35" s="39"/>
-      <c r="B35" s="43"/>
+      <c r="A35" s="29"/>
+      <c r="B35" s="34"/>
       <c r="C35" s="9" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="39">
+      <c r="A36" s="29">
         <v>17</v>
       </c>
-      <c r="B36" s="30" t="s">
+      <c r="B36" s="28" t="s">
         <v>39</v>
       </c>
       <c r="C36" s="3" t="s">
@@ -2504,14 +2522,36 @@
       </c>
     </row>
     <row r="37" spans="1:3" ht="240" x14ac:dyDescent="0.25">
-      <c r="A37" s="39"/>
-      <c r="B37" s="30"/>
+      <c r="A37" s="29"/>
+      <c r="B37" s="28"/>
       <c r="C37" s="16" t="s">
         <v>106</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
     <mergeCell ref="B36:B37"/>
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="A30:A31"/>
@@ -2524,28 +2564,6 @@
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="A32:A35"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2574,10 +2592,10 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="28">
+      <c r="A2" s="30">
         <v>1</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="28" t="s">
         <v>171</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -2585,17 +2603,17 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="28"/>
-      <c r="B3" s="30"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="28"/>
       <c r="C3" s="13" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28">
+      <c r="A4" s="30">
         <v>2</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="28" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -2603,17 +2621,17 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="165.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="28"/>
-      <c r="B5" s="30"/>
+      <c r="A5" s="30"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="3" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="28">
+      <c r="A6" s="30">
         <v>3</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="36" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="7" t="s">
@@ -2621,17 +2639,17 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="28"/>
-      <c r="B7" s="38"/>
+      <c r="A7" s="30"/>
+      <c r="B7" s="37"/>
       <c r="C7" s="8" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="28">
+      <c r="A8" s="30">
         <v>4</v>
       </c>
-      <c r="B8" s="41" t="s">
+      <c r="B8" s="32" t="s">
         <v>82</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -2639,113 +2657,102 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="28"/>
-      <c r="B9" s="42"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="33"/>
       <c r="C9" s="21" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28">
+      <c r="A10" s="30">
         <v>5</v>
       </c>
-      <c r="B10" s="42"/>
+      <c r="B10" s="33"/>
       <c r="C10" s="19" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="28"/>
-      <c r="B11" s="43"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="34"/>
       <c r="C11" s="9" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="28">
+      <c r="A12" s="30">
         <v>6</v>
       </c>
-      <c r="B12" s="28"/>
+      <c r="B12" s="30"/>
       <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
-      <c r="B13" s="28"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="30"/>
       <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="28">
+      <c r="A14" s="30">
         <v>7</v>
       </c>
-      <c r="B14" s="28"/>
+      <c r="B14" s="30"/>
       <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="28"/>
-      <c r="B15" s="28"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="30"/>
       <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28">
+      <c r="A16" s="30">
         <v>8</v>
       </c>
-      <c r="B16" s="28"/>
+      <c r="B16" s="30"/>
       <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
-      <c r="B17" s="28"/>
+      <c r="A17" s="30"/>
+      <c r="B17" s="30"/>
       <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="28">
+      <c r="A18" s="30">
         <v>9</v>
       </c>
-      <c r="B18" s="28"/>
+      <c r="B18" s="30"/>
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
-      <c r="B19" s="28"/>
+      <c r="A19" s="30"/>
+      <c r="B19" s="30"/>
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="28">
+      <c r="A20" s="30">
         <v>10</v>
       </c>
-      <c r="B20" s="28"/>
+      <c r="B20" s="30"/>
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="28"/>
-      <c r="B21" s="28"/>
+      <c r="A21" s="30"/>
+      <c r="B21" s="30"/>
       <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="28">
+      <c r="A22" s="30">
         <v>11</v>
       </c>
-      <c r="B22" s="28"/>
+      <c r="B22" s="30"/>
       <c r="C22" s="4"/>
     </row>
     <row r="23" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="28"/>
-      <c r="B23" s="28"/>
+      <c r="A23" s="30"/>
+      <c r="B23" s="30"/>
       <c r="C23" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B8:B11"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="A22:A23"/>
@@ -2756,6 +2763,17 @@
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2784,10 +2802,10 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="28">
+      <c r="A2" s="30">
         <v>1</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -2795,17 +2813,17 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="28"/>
-      <c r="B3" s="30"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="28"/>
       <c r="C3" s="3" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28">
+      <c r="A4" s="30">
         <v>2</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="28" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -2813,17 +2831,17 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="28"/>
-      <c r="B5" s="30"/>
+      <c r="A5" s="30"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="3" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="28">
+      <c r="A6" s="30">
         <v>3</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="36" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="7" t="s">
@@ -2831,17 +2849,17 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="28"/>
-      <c r="B7" s="38"/>
+      <c r="A7" s="30"/>
+      <c r="B7" s="37"/>
       <c r="C7" s="20" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="28">
+      <c r="A8" s="30">
         <v>4</v>
       </c>
-      <c r="B8" s="41" t="s">
+      <c r="B8" s="32" t="s">
         <v>82</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -2849,113 +2867,102 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="28"/>
-      <c r="B9" s="42"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="33"/>
       <c r="C9" s="22" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28">
+      <c r="A10" s="30">
         <v>5</v>
       </c>
-      <c r="B10" s="42"/>
+      <c r="B10" s="33"/>
       <c r="C10" s="19" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="28"/>
-      <c r="B11" s="43"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="34"/>
       <c r="C11" s="9" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="28">
+      <c r="A12" s="30">
         <v>6</v>
       </c>
-      <c r="B12" s="28"/>
+      <c r="B12" s="30"/>
       <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
-      <c r="B13" s="28"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="30"/>
       <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="28">
+      <c r="A14" s="30">
         <v>7</v>
       </c>
-      <c r="B14" s="28"/>
+      <c r="B14" s="30"/>
       <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="28"/>
-      <c r="B15" s="28"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="30"/>
       <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28">
+      <c r="A16" s="30">
         <v>8</v>
       </c>
-      <c r="B16" s="28"/>
+      <c r="B16" s="30"/>
       <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
-      <c r="B17" s="28"/>
+      <c r="A17" s="30"/>
+      <c r="B17" s="30"/>
       <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="28">
+      <c r="A18" s="30">
         <v>9</v>
       </c>
-      <c r="B18" s="28"/>
+      <c r="B18" s="30"/>
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
-      <c r="B19" s="28"/>
+      <c r="A19" s="30"/>
+      <c r="B19" s="30"/>
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="28">
+      <c r="A20" s="30">
         <v>10</v>
       </c>
-      <c r="B20" s="28"/>
+      <c r="B20" s="30"/>
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="28"/>
-      <c r="B21" s="28"/>
+      <c r="A21" s="30"/>
+      <c r="B21" s="30"/>
       <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="28">
+      <c r="A22" s="30">
         <v>11</v>
       </c>
-      <c r="B22" s="28"/>
+      <c r="B22" s="30"/>
       <c r="C22" s="4"/>
     </row>
     <row r="23" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="28"/>
-      <c r="B23" s="28"/>
+      <c r="A23" s="30"/>
+      <c r="B23" s="30"/>
       <c r="C23" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B8:B11"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="A22:A23"/>
@@ -2966,6 +2973,17 @@
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2994,10 +3012,10 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="28">
+      <c r="A2" s="30">
         <v>1</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="28" t="s">
         <v>42</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3005,130 +3023,332 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="28"/>
-      <c r="B3" s="30"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="28"/>
       <c r="C3" s="16" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28">
+      <c r="A4" s="30">
         <v>2</v>
       </c>
-      <c r="B4" s="30"/>
+      <c r="B4" s="28"/>
       <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="28"/>
-      <c r="B5" s="30"/>
+      <c r="A5" s="30"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="28">
+      <c r="A6" s="30">
         <v>3</v>
       </c>
-      <c r="B6" s="30"/>
+      <c r="B6" s="28"/>
       <c r="C6" s="2"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="B7" s="30"/>
+      <c r="A7" s="30"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="28">
+      <c r="A8" s="30">
         <v>4</v>
       </c>
-      <c r="B8" s="30"/>
+      <c r="B8" s="28"/>
       <c r="C8" s="2"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="28"/>
-      <c r="B9" s="30"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="28"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28">
+      <c r="A10" s="30">
         <v>5</v>
       </c>
-      <c r="B10" s="28"/>
+      <c r="B10" s="30"/>
       <c r="C10" s="2"/>
     </row>
     <row r="11" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="28"/>
-      <c r="B11" s="28"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="30"/>
       <c r="C11" s="2"/>
     </row>
     <row r="12" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="28">
+      <c r="A12" s="30">
         <v>6</v>
       </c>
-      <c r="B12" s="28"/>
+      <c r="B12" s="30"/>
       <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
-      <c r="B13" s="28"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="30"/>
       <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="28">
+      <c r="A14" s="30">
         <v>7</v>
       </c>
-      <c r="B14" s="28"/>
+      <c r="B14" s="30"/>
       <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="28"/>
-      <c r="B15" s="28"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="30"/>
       <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28">
+      <c r="A16" s="30">
         <v>8</v>
       </c>
-      <c r="B16" s="28"/>
+      <c r="B16" s="30"/>
       <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
-      <c r="B17" s="28"/>
+      <c r="A17" s="30"/>
+      <c r="B17" s="30"/>
       <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="28">
+      <c r="A18" s="30">
         <v>9</v>
       </c>
-      <c r="B18" s="28"/>
+      <c r="B18" s="30"/>
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
-      <c r="B19" s="28"/>
+      <c r="A19" s="30"/>
+      <c r="B19" s="30"/>
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="28">
+      <c r="A20" s="30">
         <v>10</v>
       </c>
-      <c r="B20" s="28"/>
+      <c r="B20" s="30"/>
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="28"/>
-      <c r="B21" s="28"/>
+      <c r="A21" s="30"/>
+      <c r="B21" s="30"/>
       <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="28">
+      <c r="A22" s="30">
         <v>11</v>
       </c>
-      <c r="B22" s="28"/>
+      <c r="B22" s="30"/>
       <c r="C22" s="4"/>
     </row>
     <row r="23" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="28"/>
-      <c r="B23" s="28"/>
+      <c r="A23" s="30"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07458B1E-2302-47BA-BCDE-62F6D02A18BC}">
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="80.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="30">
+        <v>1</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="30"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="30">
+        <v>2</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A5" s="30"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="30">
+        <v>3</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A7" s="30"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="19" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="30">
+        <v>4</v>
+      </c>
+      <c r="B8" s="28"/>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="30"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="30">
+        <v>5</v>
+      </c>
+      <c r="B10" s="30"/>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="30"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="30">
+        <v>6</v>
+      </c>
+      <c r="B12" s="30"/>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="30"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="30">
+        <v>7</v>
+      </c>
+      <c r="B14" s="30"/>
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="30"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="30">
+        <v>8</v>
+      </c>
+      <c r="B16" s="30"/>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="30"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="30">
+        <v>9</v>
+      </c>
+      <c r="B18" s="30"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="30"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="30">
+        <v>10</v>
+      </c>
+      <c r="B20" s="30"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="30"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="30">
+        <v>11</v>
+      </c>
+      <c r="B22" s="30"/>
+      <c r="C22" s="4"/>
+    </row>
+    <row r="23" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="30"/>
+      <c r="B23" s="30"/>
       <c r="C23" s="4"/>
     </row>
   </sheetData>
@@ -3162,183 +3382,949 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07458B1E-2302-47BA-BCDE-62F6D02A18BC}">
-  <dimension ref="A1:C23"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E3BCF58-CBE3-4280-BAE6-50BE357CA4D2}">
+  <dimension ref="A1:G65"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="34.42578125" customWidth="1"/>
+    <col min="3" max="3" width="51.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="30">
+        <v>1</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="30"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="30">
+        <v>2</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="30"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="30">
+        <v>3</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="30"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="30">
+        <v>3</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="30"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="30">
+        <v>4</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="30"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="45"/>
+      <c r="B12" s="46" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="42"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="30">
+        <v>5</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="30"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="30">
+        <v>6</v>
+      </c>
+      <c r="B16" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="30"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="30">
+        <v>7</v>
+      </c>
+      <c r="B18" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A19" s="30"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="45"/>
+      <c r="B20" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="42"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="30">
+        <v>8</v>
+      </c>
+      <c r="B22" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="30"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="30">
+        <v>9</v>
+      </c>
+      <c r="B24" s="47" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A25" s="30"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A26" s="11">
+        <v>10</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="11">
+        <v>11</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="30">
+        <v>12</v>
+      </c>
+      <c r="B28" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="30"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D29" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="30">
+        <v>13</v>
+      </c>
+      <c r="B30" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A31" s="30"/>
+      <c r="B31" s="44"/>
+      <c r="C31" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D31" t="e" vm="9">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E31" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F31" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G31" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="30">
+        <v>14</v>
+      </c>
+      <c r="B32" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="30"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D33" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E33" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="45">
+        <v>15</v>
+      </c>
+      <c r="B34" s="47" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A35" s="42"/>
+      <c r="B35" s="43"/>
+      <c r="C35" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="45">
+        <v>16</v>
+      </c>
+      <c r="B36" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A37" s="42"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D37" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="30">
+        <v>17</v>
+      </c>
+      <c r="B38" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="30"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="30">
+        <v>18</v>
+      </c>
+      <c r="B40" s="44"/>
+      <c r="C40" s="2"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="30"/>
+      <c r="B41" s="44"/>
+      <c r="C41" s="3"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="30">
+        <v>15</v>
+      </c>
+      <c r="B42" s="30"/>
+      <c r="C42" s="4"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="30"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="4"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="30">
+        <v>16</v>
+      </c>
+      <c r="B44" s="30"/>
+      <c r="C44" s="4"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="30"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="4"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="30">
+        <v>17</v>
+      </c>
+      <c r="B46" s="30"/>
+      <c r="C46" s="4"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="30"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="4"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="30">
+        <v>18</v>
+      </c>
+      <c r="B48" s="30"/>
+      <c r="C48" s="4"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="30"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="4"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="30">
+        <v>19</v>
+      </c>
+      <c r="B50" s="30"/>
+      <c r="C50" s="4"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="30"/>
+      <c r="B51" s="30"/>
+      <c r="C51" s="4"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="30">
+        <v>20</v>
+      </c>
+      <c r="B52" s="30"/>
+      <c r="C52" s="4"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="30"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="4"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="30">
+        <v>21</v>
+      </c>
+      <c r="B54" s="30"/>
+      <c r="C54" s="4"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="4"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="30">
+        <v>22</v>
+      </c>
+      <c r="B56" s="30"/>
+      <c r="C56" s="4"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="30"/>
+      <c r="B57" s="30"/>
+      <c r="C57" s="4"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="30">
+        <v>23</v>
+      </c>
+      <c r="B58" s="30"/>
+      <c r="C58" s="4"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="4"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="30">
+        <v>24</v>
+      </c>
+      <c r="B60" s="30"/>
+      <c r="C60" s="4"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="30"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="4"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="30">
+        <v>25</v>
+      </c>
+      <c r="B62" s="30"/>
+      <c r="C62" s="4"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="30"/>
+      <c r="B63" s="30"/>
+      <c r="C63" s="4"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="30">
+        <v>26</v>
+      </c>
+      <c r="B64" s="30"/>
+      <c r="C64" s="4"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="30"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="62">
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4897B01-73C0-4E75-A8BC-0D435AE77B79}">
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="80.42578125" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="28">
+      <c r="A2" s="38">
         <v>1</v>
       </c>
-      <c r="B2" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="28"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="9" t="s">
-        <v>119</v>
+      <c r="B2" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="39"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28">
+      <c r="A4" s="38">
         <v>2</v>
       </c>
-      <c r="B4" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.25">
-      <c r="A5" s="28"/>
-      <c r="B5" s="30"/>
-      <c r="C5" s="3" t="s">
-        <v>122</v>
+      <c r="B4" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="39"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="24" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="28">
+      <c r="A6" s="38">
         <v>3</v>
       </c>
-      <c r="B6" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="75" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="B7" s="30"/>
-      <c r="C7" s="19" t="s">
-        <v>123</v>
+      <c r="B6" s="48" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="39"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="24" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="28">
+      <c r="A8" s="38">
         <v>4</v>
       </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="28"/>
-      <c r="B9" s="30"/>
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28">
+      <c r="B8" s="48" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="39"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="42">
         <v>5</v>
       </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="28"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="2"/>
-    </row>
-    <row r="12" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="28">
+      <c r="B10" s="48" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="30"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="23" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="30">
         <v>6</v>
       </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="2"/>
-    </row>
-    <row r="13" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="2"/>
+      <c r="B12" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="30"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="23" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="14" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="28">
+      <c r="A14" s="30">
         <v>7</v>
       </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="2"/>
-    </row>
-    <row r="15" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="28"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="2"/>
+      <c r="B14" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="30"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="24" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="16" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28">
+      <c r="A16" s="30">
         <v>8</v>
       </c>
-      <c r="B16" s="28"/>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="28">
+      <c r="B16" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="30"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="30">
         <v>9</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
+      <c r="B18" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="30"/>
       <c r="B19" s="28"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="28">
+      <c r="C19" s="27" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="30">
         <v>10</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="28"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="28">
+      <c r="B20" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="30"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="30">
         <v>11</v>
       </c>
-      <c r="B22" s="28"/>
-      <c r="C22" s="4"/>
-    </row>
-    <row r="23" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="28"/>
+      <c r="B22" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A23" s="30"/>
       <c r="B23" s="28"/>
-      <c r="C23" s="4"/>
+      <c r="C23" s="16" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="30">
+        <v>12</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="132" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="30"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="18" t="e" vm="16">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="30">
+        <v>13</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A27" s="30"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="D27" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="30">
+        <v>14</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A29" s="30"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="27" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="30">
+        <v>15</v>
+      </c>
+      <c r="B30" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="135" x14ac:dyDescent="0.25">
+      <c r="A31" s="30"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="27" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="30">
+        <v>16</v>
+      </c>
+      <c r="B32" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="30"/>
+      <c r="B33" s="50"/>
+      <c r="C33" s="4" t="s">
+        <v>78</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="32">
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="A16:A17"/>
@@ -3361,12 +4347,13 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E3BCF58-CBE3-4280-BAE6-50BE357CA4D2}">
-  <dimension ref="A1:G65"/>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A47BE74F-DBF9-413C-80FF-83DC058DEDFA}">
+  <dimension ref="A1:D65"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="34.42578125" customWidth="1"/>
@@ -3385,920 +4372,401 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="28">
+      <c r="A2" s="30">
         <v>1</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="285" x14ac:dyDescent="0.25">
+      <c r="A3" s="30"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="D3" t="e" vm="18">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="30">
+        <v>2</v>
+      </c>
+      <c r="B4" s="28"/>
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="30"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="30">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="30"/>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="30">
+        <v>3</v>
+      </c>
+      <c r="B8" s="28"/>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="30"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="30">
+        <v>4</v>
+      </c>
+      <c r="B10" s="28"/>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="30"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="45"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="42"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="30">
+        <v>5</v>
+      </c>
+      <c r="B14" s="44"/>
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="30"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="30">
+        <v>6</v>
+      </c>
+      <c r="B16" s="44"/>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="30"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="30">
+        <v>7</v>
+      </c>
+      <c r="B18" s="44"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="30"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="45"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="42"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="30">
+        <v>8</v>
+      </c>
+      <c r="B22" s="44"/>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="30"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="30">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="28"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28">
-        <v>2</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="28"/>
-      <c r="B5" s="30"/>
-      <c r="C5" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D5" t="e" vm="6">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="28">
-        <v>3</v>
-      </c>
-      <c r="B6" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="B7" s="30"/>
-      <c r="C7" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="28">
-        <v>3</v>
-      </c>
-      <c r="B8" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="28"/>
-      <c r="B9" s="30"/>
-      <c r="C9" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28">
-        <v>4</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A11" s="28"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="46"/>
-      <c r="B12" s="47" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="35"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="28">
-        <v>5</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="28"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28">
-        <v>6</v>
-      </c>
-      <c r="B16" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="28">
-        <v>7</v>
-      </c>
-      <c r="B18" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="90" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="46"/>
-      <c r="B20" s="46" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="35"/>
-      <c r="B21" s="35"/>
-      <c r="C21" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="28">
-        <v>8</v>
-      </c>
-      <c r="B22" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="28"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="28">
-        <v>9</v>
-      </c>
-      <c r="B24" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A25" s="28"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="B24" s="44"/>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="30"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>10</v>
       </c>
-      <c r="B26" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B26" s="12"/>
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>11</v>
       </c>
-      <c r="B27" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="28">
+      <c r="B27" s="12"/>
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="30">
         <v>12</v>
       </c>
-      <c r="B28" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="28"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D29" t="e" vm="7">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="28">
+      <c r="B28" s="44"/>
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="30"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="30">
         <v>13</v>
       </c>
-      <c r="B30" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="105" x14ac:dyDescent="0.25">
-      <c r="A31" s="28"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D31" t="e" vm="8">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E31" t="e" vm="9">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F31" t="e" vm="10">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G31" t="e" vm="11">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="28">
+      <c r="B30" s="44"/>
+      <c r="C30" s="2"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="30"/>
+      <c r="B31" s="44"/>
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="30">
         <v>14</v>
       </c>
-      <c r="B32" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="28"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D33" t="e" vm="12">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E33" t="e" vm="13">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="46">
+      <c r="B32" s="44"/>
+      <c r="C32" s="2"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="30"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="45">
         <v>15</v>
       </c>
-      <c r="B34" s="45" t="s">
-        <v>55</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A35" s="35"/>
-      <c r="B35" s="36"/>
-      <c r="C35" s="3" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="46">
+      <c r="B34" s="47"/>
+      <c r="C34" s="2"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="42"/>
+      <c r="B35" s="43"/>
+      <c r="C35" s="3"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="45">
         <v>16</v>
       </c>
-      <c r="B36" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A37" s="35"/>
-      <c r="B37" s="36"/>
-      <c r="C37" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D37" t="e" vm="14">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="28">
+      <c r="B36" s="47"/>
+      <c r="C36" s="2"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="42"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="3"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="30">
         <v>17</v>
       </c>
-      <c r="B38" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="28"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="28">
+      <c r="B38" s="28"/>
+      <c r="C38" s="2"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="30"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="3"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="30">
         <v>18</v>
       </c>
-      <c r="B40" s="29"/>
+      <c r="B40" s="44"/>
       <c r="C40" s="2"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="28"/>
-      <c r="B41" s="29"/>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="30"/>
+      <c r="B41" s="44"/>
       <c r="C41" s="3"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="28">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="30">
         <v>15</v>
       </c>
-      <c r="B42" s="28"/>
+      <c r="B42" s="30"/>
       <c r="C42" s="4"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="28"/>
-      <c r="B43" s="28"/>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="30"/>
+      <c r="B43" s="30"/>
       <c r="C43" s="4"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="28">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="30">
         <v>16</v>
       </c>
-      <c r="B44" s="28"/>
+      <c r="B44" s="30"/>
       <c r="C44" s="4"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="28"/>
-      <c r="B45" s="28"/>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="30"/>
+      <c r="B45" s="30"/>
       <c r="C45" s="4"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="28">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="30">
         <v>17</v>
       </c>
-      <c r="B46" s="28"/>
+      <c r="B46" s="30"/>
       <c r="C46" s="4"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="28"/>
-      <c r="B47" s="28"/>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="30"/>
+      <c r="B47" s="30"/>
       <c r="C47" s="4"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="28">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="30">
         <v>18</v>
       </c>
-      <c r="B48" s="28"/>
+      <c r="B48" s="30"/>
       <c r="C48" s="4"/>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="28"/>
-      <c r="B49" s="28"/>
+      <c r="A49" s="30"/>
+      <c r="B49" s="30"/>
       <c r="C49" s="4"/>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="28">
+      <c r="A50" s="30">
         <v>19</v>
       </c>
-      <c r="B50" s="28"/>
+      <c r="B50" s="30"/>
       <c r="C50" s="4"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="28"/>
-      <c r="B51" s="28"/>
+      <c r="A51" s="30"/>
+      <c r="B51" s="30"/>
       <c r="C51" s="4"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="28">
+      <c r="A52" s="30">
         <v>20</v>
       </c>
-      <c r="B52" s="28"/>
+      <c r="B52" s="30"/>
       <c r="C52" s="4"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="28"/>
-      <c r="B53" s="28"/>
+      <c r="A53" s="30"/>
+      <c r="B53" s="30"/>
       <c r="C53" s="4"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="28">
+      <c r="A54" s="30">
         <v>21</v>
       </c>
-      <c r="B54" s="28"/>
+      <c r="B54" s="30"/>
       <c r="C54" s="4"/>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="28"/>
-      <c r="B55" s="28"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
       <c r="C55" s="4"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="28">
+      <c r="A56" s="30">
         <v>22</v>
       </c>
-      <c r="B56" s="28"/>
+      <c r="B56" s="30"/>
       <c r="C56" s="4"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="28"/>
-      <c r="B57" s="28"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="30"/>
       <c r="C57" s="4"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="28">
+      <c r="A58" s="30">
         <v>23</v>
       </c>
-      <c r="B58" s="28"/>
+      <c r="B58" s="30"/>
       <c r="C58" s="4"/>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="28"/>
-      <c r="B59" s="28"/>
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
       <c r="C59" s="4"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="28">
+      <c r="A60" s="30">
         <v>24</v>
       </c>
-      <c r="B60" s="28"/>
+      <c r="B60" s="30"/>
       <c r="C60" s="4"/>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="28"/>
-      <c r="B61" s="28"/>
+      <c r="A61" s="30"/>
+      <c r="B61" s="30"/>
       <c r="C61" s="4"/>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="28">
+      <c r="A62" s="30">
         <v>25</v>
       </c>
-      <c r="B62" s="28"/>
+      <c r="B62" s="30"/>
       <c r="C62" s="4"/>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="28"/>
-      <c r="B63" s="28"/>
+      <c r="A63" s="30"/>
+      <c r="B63" s="30"/>
       <c r="C63" s="4"/>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="28">
+      <c r="A64" s="30">
         <v>26</v>
       </c>
-      <c r="B64" s="28"/>
+      <c r="B64" s="30"/>
       <c r="C64" s="4"/>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="28"/>
-      <c r="B65" s="28"/>
+      <c r="A65" s="30"/>
+      <c r="B65" s="30"/>
       <c r="C65" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="62">
+  <mergeCells count="61">
     <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4897B01-73C0-4E75-A8BC-0D435AE77B79}">
-  <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="80.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="31">
-        <v>1</v>
-      </c>
-      <c r="B2" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="32"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="31">
-        <v>2</v>
-      </c>
-      <c r="B4" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="32"/>
-      <c r="B5" s="34"/>
-      <c r="C5" s="24" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="31">
-        <v>3</v>
-      </c>
-      <c r="B6" s="49" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="32"/>
-      <c r="B7" s="50"/>
-      <c r="C7" s="24" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="31">
-        <v>4</v>
-      </c>
-      <c r="B8" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="32"/>
-      <c r="B9" s="50"/>
-      <c r="C9" s="24" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="35">
-        <v>5</v>
-      </c>
-      <c r="B10" s="49" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="28"/>
-      <c r="B11" s="50"/>
-      <c r="C11" s="23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="28">
-        <v>6</v>
-      </c>
-      <c r="B12" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="28"/>
-      <c r="B13" s="50"/>
-      <c r="C13" s="23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="28">
-        <v>7</v>
-      </c>
-      <c r="B14" s="49" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="28"/>
-      <c r="B15" s="50"/>
-      <c r="C15" s="24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28">
-        <v>8</v>
-      </c>
-      <c r="B16" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="28">
-        <v>9</v>
-      </c>
-      <c r="B18" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="27" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="28">
-        <v>10</v>
-      </c>
-      <c r="B20" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="28"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="28">
-        <v>11</v>
-      </c>
-      <c r="B22" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A23" s="28"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="16" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="28">
-        <v>12</v>
-      </c>
-      <c r="B24" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="132" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="28"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="18" t="e" vm="15">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="28">
-        <v>13</v>
-      </c>
-      <c r="B26" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A27" s="28"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="D27" t="e" vm="16">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="28">
-        <v>14</v>
-      </c>
-      <c r="B28" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A29" s="28"/>
-      <c r="B29" s="30"/>
-      <c r="C29" s="27" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="28">
-        <v>15</v>
-      </c>
-      <c r="B30" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="135" x14ac:dyDescent="0.25">
-      <c r="A31" s="28"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="27" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="28">
-        <v>16</v>
-      </c>
-      <c r="B32" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="28"/>
-      <c r="B33" s="48"/>
-      <c r="C33" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="A10:A11"/>
@@ -4317,433 +4785,36 @@
     <mergeCell ref="B22:B23"/>
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="B30:B31"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A47BE74F-DBF9-413C-80FF-83DC058DEDFA}">
-  <dimension ref="A1:D65"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="34.42578125" customWidth="1"/>
-    <col min="3" max="3" width="51.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="28">
-        <v>1</v>
-      </c>
-      <c r="B2" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="285" x14ac:dyDescent="0.25">
-      <c r="A3" s="28"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="D3" t="e" vm="17">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28">
-        <v>2</v>
-      </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="28"/>
-      <c r="B5" s="30"/>
-      <c r="C5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="28">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="C7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="28">
-        <v>3</v>
-      </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="28"/>
-      <c r="B9" s="30"/>
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28">
-        <v>4</v>
-      </c>
-      <c r="B10" s="30"/>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="28"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="3"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="46"/>
-      <c r="B12" s="47"/>
-      <c r="C12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="35"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="3"/>
-    </row>
-    <row r="14" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="28">
-        <v>5</v>
-      </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="2"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="28"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="3"/>
-    </row>
-    <row r="16" spans="1:4" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28">
-        <v>6</v>
-      </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="28">
-        <v>7</v>
-      </c>
-      <c r="B18" s="29"/>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="3"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="46"/>
-      <c r="B20" s="46"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="35"/>
-      <c r="B21" s="35"/>
-      <c r="C21" s="3"/>
-    </row>
-    <row r="22" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="28">
-        <v>8</v>
-      </c>
-      <c r="B22" s="29"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="28"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="3"/>
-    </row>
-    <row r="24" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="28">
-        <v>9</v>
-      </c>
-      <c r="B24" s="29"/>
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="28"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="3"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="11">
-        <v>10</v>
-      </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="3"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="11">
-        <v>11</v>
-      </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="3"/>
-    </row>
-    <row r="28" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="28">
-        <v>12</v>
-      </c>
-      <c r="B28" s="29"/>
-      <c r="C28" s="2"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="28"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="28">
-        <v>13</v>
-      </c>
-      <c r="B30" s="29"/>
-      <c r="C30" s="2"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="28"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="3"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="28">
-        <v>14</v>
-      </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="2"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="28"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="3"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="46">
-        <v>15</v>
-      </c>
-      <c r="B34" s="45"/>
-      <c r="C34" s="2"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="35"/>
-      <c r="B35" s="36"/>
-      <c r="C35" s="3"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="46">
-        <v>16</v>
-      </c>
-      <c r="B36" s="45"/>
-      <c r="C36" s="2"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="35"/>
-      <c r="B37" s="36"/>
-      <c r="C37" s="3"/>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="28">
-        <v>17</v>
-      </c>
-      <c r="B38" s="30"/>
-      <c r="C38" s="2"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="28"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="3"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="28">
-        <v>18</v>
-      </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="2"/>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="28"/>
-      <c r="B41" s="29"/>
-      <c r="C41" s="3"/>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="28">
-        <v>15</v>
-      </c>
-      <c r="B42" s="28"/>
-      <c r="C42" s="4"/>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="28"/>
-      <c r="B43" s="28"/>
-      <c r="C43" s="4"/>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="28">
-        <v>16</v>
-      </c>
-      <c r="B44" s="28"/>
-      <c r="C44" s="4"/>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="28"/>
-      <c r="B45" s="28"/>
-      <c r="C45" s="4"/>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="28">
-        <v>17</v>
-      </c>
-      <c r="B46" s="28"/>
-      <c r="C46" s="4"/>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="28"/>
-      <c r="B47" s="28"/>
-      <c r="C47" s="4"/>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="28">
-        <v>18</v>
-      </c>
-      <c r="B48" s="28"/>
-      <c r="C48" s="4"/>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="28"/>
-      <c r="B49" s="28"/>
-      <c r="C49" s="4"/>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="28">
-        <v>19</v>
-      </c>
-      <c r="B50" s="28"/>
-      <c r="C50" s="4"/>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="28"/>
-      <c r="B51" s="28"/>
-      <c r="C51" s="4"/>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="28">
-        <v>20</v>
-      </c>
-      <c r="B52" s="28"/>
-      <c r="C52" s="4"/>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="28"/>
-      <c r="B53" s="28"/>
-      <c r="C53" s="4"/>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="28">
-        <v>21</v>
-      </c>
-      <c r="B54" s="28"/>
-      <c r="C54" s="4"/>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="28"/>
-      <c r="B55" s="28"/>
-      <c r="C55" s="4"/>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="28">
-        <v>22</v>
-      </c>
-      <c r="B56" s="28"/>
-      <c r="C56" s="4"/>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="28"/>
-      <c r="B57" s="28"/>
-      <c r="C57" s="4"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="28">
-        <v>23</v>
-      </c>
-      <c r="B58" s="28"/>
-      <c r="C58" s="4"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="28"/>
-      <c r="B59" s="28"/>
-      <c r="C59" s="4"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="28">
-        <v>24</v>
-      </c>
-      <c r="B60" s="28"/>
-      <c r="C60" s="4"/>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="28"/>
-      <c r="B61" s="28"/>
-      <c r="C61" s="4"/>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="28">
-        <v>25</v>
-      </c>
-      <c r="B62" s="28"/>
-      <c r="C62" s="4"/>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="28"/>
-      <c r="B63" s="28"/>
-      <c r="C63" s="4"/>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="28">
-        <v>26</v>
-      </c>
-      <c r="B64" s="28"/>
-      <c r="C64" s="4"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="28"/>
-      <c r="B65" s="28"/>
-      <c r="C65" s="4"/>
-    </row>
-  </sheetData>
-  <mergeCells count="61">
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="B56:B57"/>
     <mergeCell ref="A64:A65"/>
     <mergeCell ref="B64:B65"/>
     <mergeCell ref="A58:A59"/>
@@ -4752,59 +4823,6 @@
     <mergeCell ref="B60:B61"/>
     <mergeCell ref="A62:A63"/>
     <mergeCell ref="B62:B63"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B2:B3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
